--- a/data/patnet_aichi_archive.xlsx
+++ b/data/patnet_aichi_archive.xlsx
@@ -10,7 +10,7 @@
     <sheet name="incidents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$947</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$948</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N947"/>
+  <dimension ref="A1:N948"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -64866,8 +64866,76 @@
         </is>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>d5a85209b9dbc24600d8</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>10月26日(月)午後3時15分頃</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>犬山市</t>
+        </is>
+      </c>
+      <c r="F948" s="2" t="inlineStr">
+        <is>
+          <t>犬山市付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>犬山市</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I948" t="n">
+        <v>35.378441</v>
+      </c>
+      <c r="J948" t="n">
+        <v>136.944427</v>
+      </c>
+      <c r="K948" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L948" s="3" t="inlineStr">
+        <is>
+          <t>2人組のうち1名の男が帰宅中の男子生徒に対して、「こっち来たらお菓子あげるよ」と声をかけた</t>
+        </is>
+      </c>
+      <c r="M948" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/26/%e7%8a%ac%e5%b1%b1%e5%b8%82-110/</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>2026-10-27T00:30:43+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N947"/>
+  <autoFilter ref="A1:N948"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -65815,6 +65883,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M945" r:id="rId944"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M946" r:id="rId945"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M947" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M948" r:id="rId947"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/patnet_aichi_archive.xlsx
+++ b/data/patnet_aichi_archive.xlsx
@@ -10,7 +10,7 @@
     <sheet name="incidents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$948</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$950</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N948"/>
+  <dimension ref="A1:N950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -64934,8 +64934,144 @@
         </is>
       </c>
     </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>5d6d7076d6c03eb5dc65</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>10月27日(火)午後5時20分頃</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区</t>
+        </is>
+      </c>
+      <c r="F949" s="2" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>名古屋市昭和区</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I949" t="n">
+        <v>35.150276</v>
+      </c>
+      <c r="J949" t="n">
+        <v>136.934174</v>
+      </c>
+      <c r="K949" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L949" s="3" t="inlineStr">
+        <is>
+          <t>男が、自転車で走行中の女子児童の後をつけた</t>
+        </is>
+      </c>
+      <c r="M949" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/27/%e5%90%8d%e5%8f%a4%e5%b1%8b%e5%b8%82%e6%98%ad%e5%92%8c%e5%8c%ba-200/</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>2026-10-28T00:35:46+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>85da54d3aaaf65c302b6</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>10月27日（火)午後4時頃</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区</t>
+        </is>
+      </c>
+      <c r="F950" s="2" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I950" t="n">
+        <v>35.131397</v>
+      </c>
+      <c r="J950" t="n">
+        <v>136.934982</v>
+      </c>
+      <c r="K950" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L950" s="3" t="inlineStr">
+        <is>
+          <t>男が中学生に対して「何でこんな時間に帰ってきてるんだ。普通だったら考えられんだろう」等と声を掛けた</t>
+        </is>
+      </c>
+      <c r="M950" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/27/%e5%90%8d%e5%8f%a4%e5%b1%8b%e5%b8%82%e7%91%9e%e7%a9%82%e5%8c%ba-72/</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>2026-10-28T00:35:47+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N948"/>
+  <autoFilter ref="A1:N950"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -65884,6 +66020,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M946" r:id="rId945"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M947" r:id="rId946"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M948" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M949" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M950" r:id="rId949"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/patnet_aichi_archive.xlsx
+++ b/data/patnet_aichi_archive.xlsx
@@ -10,7 +10,7 @@
     <sheet name="incidents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$950</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$952</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N950"/>
+  <dimension ref="A1:N952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -65070,8 +65070,144 @@
         </is>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>fa22c1831398beecceb1</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>10月28日(水)午後6時50分頃</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>小牧市</t>
+        </is>
+      </c>
+      <c r="F951" s="2" t="inlineStr">
+        <is>
+          <t>小牧市付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>小牧市</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I951" t="n">
+        <v>35.29044</v>
+      </c>
+      <c r="J951" t="n">
+        <v>136.910995</v>
+      </c>
+      <c r="K951" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L951" s="3" t="inlineStr">
+        <is>
+          <t>男が自転車で帰宅途中の女子生徒の後をつけた</t>
+        </is>
+      </c>
+      <c r="M951" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/28/%e5%b0%8f%e7%89%a7%e5%b8%82-465/</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:02:28+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>7fe79f2d03cb7f124bbc</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>10月26日(月)午前8時頃</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>小牧市</t>
+        </is>
+      </c>
+      <c r="F952" s="2" t="inlineStr">
+        <is>
+          <t>小牧市付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>小牧市</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I952" t="n">
+        <v>35.29044</v>
+      </c>
+      <c r="J952" t="n">
+        <v>136.910995</v>
+      </c>
+      <c r="K952" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L952" s="3" t="inlineStr">
+        <is>
+          <t>女が登校中の児童らに対し、スマートフォンのカメラレンズを向けた</t>
+        </is>
+      </c>
+      <c r="M952" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/26/%e5%b0%8f%e7%89%a7%e5%b8%82-463/</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:02:29+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N950"/>
+  <autoFilter ref="A1:N952"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -66022,6 +66158,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M948" r:id="rId947"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M949" r:id="rId948"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M950" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M951" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M952" r:id="rId951"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/patnet_aichi_archive.xlsx
+++ b/data/patnet_aichi_archive.xlsx
@@ -10,7 +10,7 @@
     <sheet name="incidents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$952</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$958</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N952"/>
+  <dimension ref="A1:N958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -65206,8 +65206,416 @@
         </is>
       </c>
     </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>ec9f0fc675bd07583b93</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>不審者情報 , 身近な犯罪情報</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>名古屋市東区</t>
+        </is>
+      </c>
+      <c r="F953" s="2" t="inlineStr">
+        <is>
+          <t>名古屋市東区付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>名古屋市東区</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I953" t="n">
+        <v>35.179325</v>
+      </c>
+      <c r="J953" t="n">
+        <v>136.926056</v>
+      </c>
+      <c r="K953" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L953" s="3" t="inlineStr">
+        <is>
+          <t>不審な人物に関する情報です。詳しい状況は掲載元の記事をご確認ください。</t>
+        </is>
+      </c>
+      <c r="M953" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/29/%e5%90%8d%e5%8f%a4%e5%b1%8b%e5%b8%82%e6%9d%b1%e5%8c%ba-128/</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:03:50+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>1faa54de93f7533dd3b7</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>10月29日(木)午後2時50分頃</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>名古屋市瑞穂区</t>
+        </is>
+      </c>
+      <c r="F954" s="2" t="inlineStr">
+        <is>
+          <t>瑞穂区初日町付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>瑞穂区初日町</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I954" t="n">
+        <v>35.18021</v>
+      </c>
+      <c r="J954" t="n">
+        <v>136.906586</v>
+      </c>
+      <c r="K954" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L954" s="3" t="inlineStr">
+        <is>
+          <t>男が児童とすれ違った後に「おい、お前だ」と叫んだもの。</t>
+        </is>
+      </c>
+      <c r="M954" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/29/%e5%90%8d%e5%8f%a4%e5%b1%8b%e5%b8%82%e7%91%9e%e7%a9%82%e5%8c%ba-73/</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:03:51+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>28dd9907a0fc5b1b30c9</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>安城市</t>
+        </is>
+      </c>
+      <c r="F955" s="2" t="inlineStr">
+        <is>
+          <t>安城市付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>安城市</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I955" t="n">
+        <v>34.958614</v>
+      </c>
+      <c r="J955" t="n">
+        <v>137.080276</v>
+      </c>
+      <c r="K955" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L955" s="3" t="inlineStr">
+        <is>
+          <t>安城市</t>
+        </is>
+      </c>
+      <c r="M955" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/28/%e5%ae%89%e5%9f%8e%e5%b8%82-200/</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:03:52+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>ee1b2f0a4bc725da7cb4</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>10月28日(水)午後5時頃</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>安城市</t>
+        </is>
+      </c>
+      <c r="F956" s="2" t="inlineStr">
+        <is>
+          <t>安城市桜井町付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>安城市桜井町</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I956" t="n">
+        <v>34.92458</v>
+      </c>
+      <c r="J956" t="n">
+        <v>137.094269</v>
+      </c>
+      <c r="K956" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L956" s="3" t="inlineStr">
+        <is>
+          <t>買い物中の児童に、暴言を吐いた</t>
+        </is>
+      </c>
+      <c r="M956" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/28/%e5%ae%89%e5%9f%8e%e5%b8%82-199/</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:03:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>6b244e14aed108058466</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>10月28日(水)午後4時頃</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>不審者情報 , 身近な犯罪情報</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="F957" s="2" t="inlineStr">
+        <is>
+          <t>名古屋市千種区付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I957" t="n">
+        <v>35.162659</v>
+      </c>
+      <c r="J957" t="n">
+        <v>136.977615</v>
+      </c>
+      <c r="K957" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L957" s="3" t="inlineStr">
+        <is>
+          <t>男が女子生徒に携帯電話を向けたり、スカートを覗き込むように屈んだりしていた</t>
+        </is>
+      </c>
+      <c r="M957" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/28/%e5%90%8d%e5%8f%a4%e5%b1%8b%e5%b8%82%e5%8d%83%e7%a8%ae%e5%8c%ba-259/</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:03:54+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>e6ca55710016eb5dc6ec</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>10月28日(水)午後3時30分頃</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>不審者情報 , 身近な犯罪情報</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>豊川市</t>
+        </is>
+      </c>
+      <c r="F958" s="2" t="inlineStr">
+        <is>
+          <t>豊川市桜町付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>豊川市桜町</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I958" t="n">
+        <v>34.81638</v>
+      </c>
+      <c r="J958" t="n">
+        <v>137.349426</v>
+      </c>
+      <c r="K958" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L958" s="3" t="inlineStr">
+        <is>
+          <t>男が道路沿いに下半身を露出して立っていた。</t>
+        </is>
+      </c>
+      <c r="M958" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/28/%e8%b1%8a%e5%b7%9d%e5%b8%82-144/</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>2026-10-30T01:03:55+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N952"/>
+  <autoFilter ref="A1:N958"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -66160,6 +66568,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M950" r:id="rId949"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M951" r:id="rId950"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M952" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M953" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M954" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M955" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M956" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M957" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M958" r:id="rId957"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/patnet_aichi_archive.xlsx
+++ b/data/patnet_aichi_archive.xlsx
@@ -10,7 +10,7 @@
     <sheet name="incidents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$958</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'incidents'!$A$1:$N$962</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N958"/>
+  <dimension ref="A1:N962"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -65614,8 +65614,280 @@
         </is>
       </c>
     </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>082230b7d1e64e6046aa</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>10月30日(金)午後4時30分頃</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>不審者情報 , 身近な犯罪情報</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>春日井市</t>
+        </is>
+      </c>
+      <c r="F959" s="2" t="inlineStr">
+        <is>
+          <t>春日井市八田町付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>春日井市八田町</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I959" t="n">
+        <v>35.250999</v>
+      </c>
+      <c r="J959" t="n">
+        <v>136.969925</v>
+      </c>
+      <c r="K959" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L959" s="3" t="inlineStr">
+        <is>
+          <t>男が女性に向かって下半身を出し放尿した</t>
+        </is>
+      </c>
+      <c r="M959" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/30/%e6%98%a5%e6%97%a5%e4%ba%95%e5%b8%82-132/</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:52:33+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>0195784b87d0b1bdf910</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>10月29日(木)午後10時10分頃</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>西尾市</t>
+        </is>
+      </c>
+      <c r="F960" s="2" t="inlineStr">
+        <is>
+          <t>西尾市一色町付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>西尾市一色町</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I960" t="n">
+        <v>34.810116</v>
+      </c>
+      <c r="J960" t="n">
+        <v>137.024948</v>
+      </c>
+      <c r="K960" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L960" s="3" t="inlineStr">
+        <is>
+          <t>見知らぬ男が、帰宅中の女子高校生に「ねぇ」等と声をかけた</t>
+        </is>
+      </c>
+      <c r="M960" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/29/%e8%a5%bf%e5%b0%be%e5%b8%82-274/</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:52:35+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>5dd9e4fa9ea715bfee92</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>10月29日(木)午後4時30分頃</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>豊田市</t>
+        </is>
+      </c>
+      <c r="F961" s="2" t="inlineStr">
+        <is>
+          <t>豊田市付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>豊田市</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I961" t="n">
+        <v>35.082565</v>
+      </c>
+      <c r="J961" t="n">
+        <v>137.156235</v>
+      </c>
+      <c r="K961" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L961" s="3" t="inlineStr">
+        <is>
+          <t>男が、女子小学生に対し無言で手招きをしたもの。</t>
+        </is>
+      </c>
+      <c r="M961" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/29/%e8%b1%8a%e7%94%b0%e5%b8%82-209/</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:52:36+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>9d22f616f5be69b48855</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>10月29日午前9時15分～午前9時30分頃</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>不審者情報</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="F962" s="2" t="inlineStr">
+        <is>
+          <t>名古屋市千種区付近（地域代表点）</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>名古屋市千種区</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>municipality</t>
+        </is>
+      </c>
+      <c r="I962" t="n">
+        <v>35.162659</v>
+      </c>
+      <c r="J962" t="n">
+        <v>136.977615</v>
+      </c>
+      <c r="K962" s="3" t="inlineStr">
+        <is>
+          <t>声かけ・不審者情報に関する情報です。</t>
+        </is>
+      </c>
+      <c r="L962" s="3" t="inlineStr">
+        <is>
+          <t>不審者2名がスマホのカメラレンズを住宅に向けていた</t>
+        </is>
+      </c>
+      <c r="M962" s="4" t="inlineStr">
+        <is>
+          <t>http://patnet.jp/2026/10/29/%e5%90%8d%e5%8f%a4%e5%b1%8b%e5%b8%82%e5%8d%83%e7%a8%ae%e5%8c%ba-260/</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:52:38+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N958"/>
+  <autoFilter ref="A1:N962"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId2"/>
@@ -66574,6 +66846,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M956" r:id="rId955"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M957" r:id="rId956"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M958" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M959" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M960" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M961" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M962" r:id="rId961"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
